--- a/QLNS/bin/Debug/FileExcels/SK_DanhSachCanBo_02.xlsx
+++ b/QLNS/bin/Debug/FileExcels/SK_DanhSachCanBo_02.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBSP_DEV\AZUREDEPOPS_PROJECT\VBSP-QLNS\VBSP-QLNS\QLNS\FileExcels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="96" windowWidth="20112" windowHeight="8520"/>
   </bookViews>
@@ -17,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>STT</t>
   </si>
@@ -413,6 +418,12 @@
   </si>
   <si>
     <t>%NgayBoNhiemLai_HT</t>
+  </si>
+  <si>
+    <t>%DonVi_Moi_HT</t>
+  </si>
+  <si>
+    <t>%ChiNhanh_HT</t>
   </si>
 </sst>
 </file>
@@ -592,6 +603,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -639,7 +653,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -674,7 +688,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -883,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR3"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.21875" style="1" customWidth="1"/>
@@ -922,7 +936,7 @@
     <col min="45" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="3" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:46" s="3" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1056,7 +1070,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:44" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:46" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1190,7 +1204,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:44" s="3" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:46" s="3" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
@@ -1322,6 +1336,12 @@
       </c>
       <c r="AR3" s="13" t="s">
         <v>127</v>
+      </c>
+      <c r="AS3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AT3" s="9" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
